--- a/Luban/Datas/Bullet.xlsx
+++ b/Luban/Datas/Bullet.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1435,6 +1435,77 @@
         <v>0</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>level1_midboss_sway_windmill_bullet</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Sway:0.34,1.45,55,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Assets/Art/Sprites/Bullets/enemy_bullet_43.png</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/Bullet.xlsx
+++ b/Luban/Datas/Bullet.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1506,6 +1506,148 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>boss_s_windmill_bullet</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Sway:0.58,1.25,85,0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Assets/Art/Sprites/Bullets/enemy_bullet_43.png</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>boss_s_windmill_bullet_big</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Sway:0.82,1.1,105,0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Assets/Art/Sprites/Bullets/enemy_bullet_43.png</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/Bullet.xlsx
+++ b/Luban/Datas/Bullet.xlsx
@@ -534,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12.33203125" customWidth="1" style="1" min="1" max="2"/>
@@ -1648,6 +1648,76 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>level2_helicopter_bullet_29</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enemy</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Single:GlowTrail</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Assets/Art/Sprites/Bullets/enemy_bullet_29.png</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Luban/Datas/Bullet.xlsx
+++ b/Luban/Datas/Bullet.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet" sheetId="1" r:id="R42759f5cb00f464a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet" sheetId="1" r:id="Rea9c91bcf4254568"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1590,7 +1590,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I16" t="n">
-        <x:v>2</x:v>
+        <x:v>0.8</x:v>
       </x:c>
       <x:c r="J16" t="n">
         <x:v>0.28</x:v>
@@ -1602,10 +1602,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M16" t="n">
-        <x:v>0.78</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="N16" t="n">
-        <x:v>0.08</x:v>
+        <x:v>0.04</x:v>
       </x:c>
       <x:c r="O16" t="n">
         <x:v>0.9</x:v>

--- a/Luban/Datas/Bullet.xlsx
+++ b/Luban/Datas/Bullet.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet" sheetId="1" r:id="Rea9c91bcf4254568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bullet" sheetId="1" r:id="R72ddee210c1546e4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1116,16 +1116,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M9" s="2" t="n">
-        <x:v>0.48</x:v>
+        <x:v>0.217</x:v>
       </x:c>
       <x:c r="N9" s="2" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.321</x:v>
       </x:c>
       <x:c r="O9" s="2" t="n">
-        <x:v>0.58</x:v>
+        <x:v>0.62</x:v>
       </x:c>
       <x:c r="P9" s="2" t="n">
-        <x:v>0.18</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="Q9" s="2" t="n">
         <x:v>1</x:v>
@@ -1187,16 +1187,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M10" s="2" t="n">
-        <x:v>0.32</x:v>
+        <x:v>0.217</x:v>
       </x:c>
       <x:c r="N10" s="2" t="n">
-        <x:v>0.12</x:v>
+        <x:v>0.321</x:v>
       </x:c>
       <x:c r="O10" s="2" t="n">
-        <x:v>0.5</x:v>
+        <x:v>0.56</x:v>
       </x:c>
       <x:c r="P10" s="2" t="n">
-        <x:v>0.16</x:v>
+        <x:v>0.18</x:v>
       </x:c>
       <x:c r="Q10" s="2" t="n">
         <x:v>1</x:v>
@@ -1258,16 +1258,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M11" s="2" t="n">
-        <x:v>0.38</x:v>
+        <x:v>0.251</x:v>
       </x:c>
       <x:c r="N11" s="2" t="n">
-        <x:v>0.16</x:v>
+        <x:v>0.596</x:v>
       </x:c>
       <x:c r="O11" s="2" t="n">
-        <x:v>0.52</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="P11" s="2" t="n">
-        <x:v>0.18</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="Q11" s="2" t="n">
         <x:v>1</x:v>
@@ -1329,16 +1329,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M12" s="2" t="n">
-        <x:v>0.38</x:v>
+        <x:v>0.251</x:v>
       </x:c>
       <x:c r="N12" s="2" t="n">
-        <x:v>0.16</x:v>
+        <x:v>0.596</x:v>
       </x:c>
       <x:c r="O12" s="2" t="n">
-        <x:v>0.52</x:v>
+        <x:v>0.64</x:v>
       </x:c>
       <x:c r="P12" s="2" t="n">
-        <x:v>0.18</x:v>
+        <x:v>0.22</x:v>
       </x:c>
       <x:c r="Q12" s="2" t="n">
         <x:v>1</x:v>
@@ -1397,19 +1397,19 @@
         <x:v>0.34</x:v>
       </x:c>
       <x:c r="L13" s="2" t="n">
-        <x:v>0.86</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M13" s="2" t="n">
-        <x:v>0.32</x:v>
+        <x:v>0.251</x:v>
       </x:c>
       <x:c r="N13" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>0.596</x:v>
       </x:c>
       <x:c r="O13" s="2" t="n">
-        <x:v>0.55</x:v>
+        <x:v>0.68</x:v>
       </x:c>
       <x:c r="P13" s="2" t="n">
-        <x:v>0.2</x:v>
+        <x:v>0.24</x:v>
       </x:c>
       <x:c r="Q13" s="2" t="n">
         <x:v>1</x:v>
@@ -1468,19 +1468,19 @@
         <x:v>0.38</x:v>
       </x:c>
       <x:c r="L14" s="2" t="n">
-        <x:v>0.86</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M14" s="2" t="n">
-        <x:v>0.22</x:v>
+        <x:v>0.251</x:v>
       </x:c>
       <x:c r="N14" s="2" t="n">
-        <x:v>1</x:v>
+        <x:v>0.596</x:v>
       </x:c>
       <x:c r="O14" s="2" t="n">
-        <x:v>0.62</x:v>
+        <x:v>0.74</x:v>
       </x:c>
       <x:c r="P14" s="2" t="n">
-        <x:v>0.24</x:v>
+        <x:v>0.28</x:v>
       </x:c>
       <x:c r="Q14" s="2" t="n">
         <x:v>1</x:v>
@@ -1538,19 +1538,19 @@
         <x:v>0.42</x:v>
       </x:c>
       <x:c r="L15" t="n">
-        <x:v>0.78</x:v>
+        <x:v>0.729</x:v>
       </x:c>
       <x:c r="M15" t="n">
+        <x:v>0.406</x:v>
+      </x:c>
+      <x:c r="N15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O15" t="n">
+        <x:v>0.72</x:v>
+      </x:c>
+      <x:c r="P15" t="n">
         <x:v>0.28</x:v>
-      </x:c>
-      <x:c r="N15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" t="n">
-        <x:v>0.68</x:v>
-      </x:c>
-      <x:c r="P15" t="n">
-        <x:v>0.25</x:v>
       </x:c>
       <x:c r="Q15" t="n">
         <x:v>1</x:v>
